--- a/artfynd/A 36428-2021 artfynd.xlsx
+++ b/artfynd/A 36428-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36428-2021 artfynd.xlsx
+++ b/artfynd/A 36428-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73695341</v>
+        <v>89140775</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öst om 7:4, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447661.9635505551</v>
+        <v>447628</v>
       </c>
       <c r="R2" t="n">
-        <v>6430316.822418524</v>
+        <v>6430229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,58 +760,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Sandbarrsvampar</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73695342</v>
+        <v>73695339</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447683.1604800681</v>
+        <v>447613</v>
       </c>
       <c r="R3" t="n">
-        <v>6430313.895122685</v>
+        <v>6430331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +853,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,16 +889,11 @@
         <v>73695340</v>
       </c>
       <c r="B4" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -974,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447646.0676097745</v>
+        <v>447646</v>
       </c>
       <c r="R4" t="n">
-        <v>6430319.150410464</v>
+        <v>6430319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,19 +963,9 @@
           <t>2018-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,59 +996,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73695338</v>
+        <v>80282904</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öst om 7:4, Vg</t>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447578.8798210627</v>
+        <v>447613</v>
       </c>
       <c r="R5" t="n">
-        <v>6430336.988392593</v>
+        <v>6430317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,22 +1068,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-18</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,13 +1092,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1169,64 +1109,61 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Sandbarrsvampar</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79773074</v>
+        <v>80283511</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447579.3778072942</v>
+        <v>447828</v>
       </c>
       <c r="R6" t="n">
-        <v>6430294.0615041</v>
+        <v>6430221</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,22 +1187,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1296,55 +1234,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79773026</v>
+        <v>89140770</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447646.9276715819</v>
+        <v>447638</v>
       </c>
       <c r="R7" t="n">
-        <v>6430303.772577518</v>
+        <v>6430318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,22 +1308,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,35 +1328,30 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80283511</v>
+        <v>89140776</v>
       </c>
       <c r="B8" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1452,25 +1374,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447827.9371242233</v>
+        <v>447605</v>
       </c>
       <c r="R8" t="n">
-        <v>6430220.859657295</v>
+        <v>6430323</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1418,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,42 +1432,36 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf, Helena Uhlén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80282904</v>
+        <v>97758145</v>
       </c>
       <c r="B9" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1574,24 +1482,17 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447613.1238046383</v>
+        <v>447558</v>
       </c>
       <c r="R9" t="n">
-        <v>6430316.933259942</v>
+        <v>6430342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,22 +1519,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,78 +1533,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79773059</v>
+        <v>97758147</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447611.4618939706</v>
+        <v>447579</v>
       </c>
       <c r="R10" t="n">
-        <v>6430311.656264145</v>
+        <v>6430340</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,22 +1625,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,69 +1645,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87799703</v>
+        <v>97758149</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öst om 7:4, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447646.0676097745</v>
+        <v>447610</v>
       </c>
       <c r="R11" t="n">
-        <v>6430319.150410464</v>
+        <v>6430326</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,22 +1731,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,76 +1745,63 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87799707</v>
+        <v>97758151</v>
       </c>
       <c r="B12" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öst om 7:4, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447646.0676097745</v>
+        <v>447644</v>
       </c>
       <c r="R12" t="n">
-        <v>6430319.150410464</v>
+        <v>6430320</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,22 +1828,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,76 +1842,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87799700</v>
+        <v>97758154</v>
       </c>
       <c r="B13" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öst om 7:4, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447646.0676097745</v>
+        <v>447711</v>
       </c>
       <c r="R13" t="n">
-        <v>6430319.150410464</v>
+        <v>6430286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,22 +1925,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,82 +1939,63 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89140765</v>
+        <v>97758156</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447766.7451938009</v>
+        <v>447739</v>
       </c>
       <c r="R14" t="n">
-        <v>6430250.803929267</v>
+        <v>6430305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2225,22 +2022,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2255,66 +2042,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89140769</v>
+        <v>103521361</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Hökensås 500 m V Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447653.9599936051</v>
+        <v>447624</v>
       </c>
       <c r="R15" t="n">
-        <v>6430313.748091802</v>
+        <v>6430322</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2341,22 +2126,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera platser utmed vägen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,81 +2145,64 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89140777</v>
+        <v>97758148</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447573.0272286284</v>
+        <v>447586</v>
       </c>
       <c r="R16" t="n">
-        <v>6430336.005506604</v>
+        <v>6430336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2466,22 +2229,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,75 +2249,64 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89140772</v>
+        <v>103521370</v>
       </c>
       <c r="B17" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Hökensås 500 m V Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447568.9865064513</v>
+        <v>447624</v>
       </c>
       <c r="R17" t="n">
-        <v>6430270.883039245</v>
+        <v>6430322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2591,22 +2333,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Utmed vägen, främst ca 20 m från beståndsgräns utmed södra vägkanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,37 +2352,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
-        </is>
-      </c>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89140768</v>
+        <v>87799700</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2653,43 +2382,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Öst om 7:4, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447700.0486253637</v>
+        <v>447646</v>
       </c>
       <c r="R18" t="n">
-        <v>6430306.255463383</v>
+        <v>6430319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2716,22 +2439,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2740,6 +2453,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2465,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2762,15 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89140770</v>
+        <v>73695338</v>
       </c>
       <c r="B19" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2778,26 +2487,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2807,14 +2516,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Öst om 7:4, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447638.0918452788</v>
+        <v>447579</v>
       </c>
       <c r="R19" t="n">
-        <v>6430318.195274085</v>
+        <v>6430337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,22 +2550,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2871,35 +2570,30 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Sandbarrsvampar</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89140771</v>
+        <v>73695341</v>
       </c>
       <c r="B20" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2922,7 +2616,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2932,14 +2626,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Öst om 7:4, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447638.0918452788</v>
+        <v>447662</v>
       </c>
       <c r="R20" t="n">
-        <v>6430318.195274085</v>
+        <v>6430317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2966,22 +2660,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2996,35 +2680,30 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Sandbarrsvampar</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89140766</v>
+        <v>79773026</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3047,24 +2726,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447713.75901258</v>
+        <v>447647</v>
       </c>
       <c r="R21" t="n">
-        <v>6430299.187371799</v>
+        <v>6430304</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3091,22 +2766,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3121,35 +2796,30 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89140767</v>
+        <v>79773059</v>
       </c>
       <c r="B22" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3172,24 +2842,20 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447707.9549878571</v>
+        <v>447611</v>
       </c>
       <c r="R22" t="n">
-        <v>6430301.91281833</v>
+        <v>6430312</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3216,22 +2882,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3246,35 +2912,30 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89140764</v>
+        <v>79773074</v>
       </c>
       <c r="B23" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3297,24 +2958,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447774.1417329889</v>
+        <v>447579</v>
       </c>
       <c r="R23" t="n">
-        <v>6430248.057699717</v>
+        <v>6430294</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3341,22 +2998,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3371,31 +3028,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89140776</v>
+        <v>87799703</v>
       </c>
       <c r="B24" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3403,43 +3055,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster om Axtorp, Vg</t>
+          <t>Öst om 7:4, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447605.2384354944</v>
+        <v>447646</v>
       </c>
       <c r="R24" t="n">
-        <v>6430322.865444668</v>
+        <v>6430319</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3466,22 +3112,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3490,6 +3126,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3501,7 +3138,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Staaf, Helena Uhlén</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3512,19 +3149,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97758150</v>
+        <v>89140764</v>
       </c>
       <c r="B25" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3547,7 +3179,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3557,14 +3189,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sveds tallskog, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447610.5950170739</v>
+        <v>447774</v>
       </c>
       <c r="R25" t="n">
-        <v>6430326.504289049</v>
+        <v>6430248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3591,22 +3223,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3621,27 +3243,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97758149</v>
+        <v>89140765</v>
       </c>
       <c r="B26" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3649,26 +3270,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3678,14 +3299,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sveds tallskog, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447610.5950170739</v>
+        <v>447767</v>
       </c>
       <c r="R26" t="n">
-        <v>6430326.504289049</v>
+        <v>6430251</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3712,22 +3333,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,27 +3353,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97758154</v>
+        <v>89140766</v>
       </c>
       <c r="B27" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3770,34 +3380,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sveds tallskog, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447710.9245927767</v>
+        <v>447714</v>
       </c>
       <c r="R27" t="n">
-        <v>6430285.447535466</v>
+        <v>6430299</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3824,22 +3443,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3854,27 +3463,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97758151</v>
+        <v>89140767</v>
       </c>
       <c r="B28" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3882,34 +3490,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sveds tallskog, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447643.4206044882</v>
+        <v>447708</v>
       </c>
       <c r="R28" t="n">
-        <v>6430319.715011469</v>
+        <v>6430302</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3936,22 +3553,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,27 +3573,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elinor Molinari</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103521339</v>
+        <v>89140768</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3994,41 +3600,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hökensås 500 m V Axtorp, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447624.3468932553</v>
+        <v>447700</v>
       </c>
       <c r="R29" t="n">
-        <v>6430322.614654041</v>
+        <v>6430306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4055,27 +3663,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>I södra vägkanten ca 20 m från beståndsgräns</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4084,34 +3677,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103521361</v>
+        <v>89140769</v>
       </c>
       <c r="B30" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4119,41 +3710,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hökensås 500 m V Axtorp, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447624.3468932553</v>
+        <v>447654</v>
       </c>
       <c r="R30" t="n">
-        <v>6430322.614654041</v>
+        <v>6430314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4180,27 +3764,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera platser utmed vägen</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4209,34 +3778,32 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103521370</v>
+        <v>89140771</v>
       </c>
       <c r="B31" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,41 +3811,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hökensås 500 m V Axtorp, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447624.3468932553</v>
+        <v>447638</v>
       </c>
       <c r="R31" t="n">
-        <v>6430322.614654041</v>
+        <v>6430318</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4305,27 +3874,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Utmed vägen, främst ca 20 m från beståndsgräns utmed södra vägkanten.</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4334,38 +3888,36 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103521347</v>
+        <v>89140772</v>
       </c>
       <c r="B32" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4388,22 +3940,24 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hökensås 500 m V Axtorp, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447624.3468932553</v>
+        <v>447569</v>
       </c>
       <c r="R32" t="n">
-        <v>6430322.614654041</v>
+        <v>6430271</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4430,27 +3984,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs vägen utmed hela beståndet</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4459,80 +3998,67 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103711534</v>
+        <v>89140773</v>
       </c>
       <c r="B33" t="n">
-        <v>88042</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hökensås 500 m V Axtorp, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447624.3468932553</v>
+        <v>447574</v>
       </c>
       <c r="R33" t="n">
-        <v>6430322.614654041</v>
+        <v>6430221</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4559,22 +4085,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4583,34 +4099,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112269372</v>
+        <v>89140777</v>
       </c>
       <c r="B34" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4618,26 +4132,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4645,21 +4159,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>800 m V Axtorp, Vg</t>
+          <t>Väster om Axtorp, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447837</v>
+        <v>447573</v>
       </c>
       <c r="R34" t="n">
-        <v>6430211</v>
+        <v>6430336</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4683,12 +4195,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4697,22 +4209,1301 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>89140778</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Väster om Axtorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>447571</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6430342</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Helena Uhlén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>97758146</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sveds tallskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>447567</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6430342</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>97758150</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sveds tallskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>447610</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6430326</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>97758152</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sveds tallskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>447681</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6430316</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>97758153</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sveds tallskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>447692</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6430316</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>103521347</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hökensås 500 m V Axtorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>447624</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6430322</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs vägen utmed hela beståndet</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Niklas Johansson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Niklas Johansson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80282836</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>447717</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6430323</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2019-10-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2019-10-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>87799707</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Öst om 7:4, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>447646</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6430319</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>73695342</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öst om 7:4, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>447683</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6430314</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>73695343</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Öst om 7:4, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>447741</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6430302</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Sandbarrsvampar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>97758155</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sveds tallskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>447733</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6430301</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>103711534</v>
+      </c>
+      <c r="B46" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hökensås 500 m V Axtorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>447624</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6430322</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
